--- a/resources/templates/standard/F2100-10.xlsx
+++ b/resources/templates/standard/F2100-10.xlsx
@@ -15,7 +15,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="117">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>작업자 숙련도 CHECK SHEET</t>
   </si>
@@ -2034,10 +2037,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -2058,16 +2063,16 @@
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
       <c r="V1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" ht="20.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -2153,14 +2158,14 @@
     </row>
     <row r="5" ht="20.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -2169,10 +2174,10 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
@@ -2184,7 +2189,7 @@
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
       <c r="V5" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W5" s="9"/>
       <c r="X5" s="9"/>
@@ -2222,20 +2227,20 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
@@ -2254,14 +2259,14 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
@@ -2269,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
@@ -2302,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I9" s="24"/>
       <c r="J9" s="24"/>
@@ -2335,7 +2340,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I10" s="24"/>
       <c r="J10" s="24"/>
@@ -2368,7 +2373,7 @@
         <v>4</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="24"/>
@@ -2401,7 +2406,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="24"/>
       <c r="J12" s="24"/>
@@ -2434,7 +2439,7 @@
         <v>6</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
@@ -2467,7 +2472,7 @@
       <c r="H14" s="35"/>
       <c r="I14" s="35"/>
       <c r="J14" s="36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K14" s="37"/>
       <c r="L14" s="38">
@@ -2510,7 +2515,7 @@
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
@@ -2518,7 +2523,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I15" s="41"/>
       <c r="J15" s="41"/>
@@ -2551,7 +2556,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I16" s="24"/>
       <c r="J16" s="24"/>
@@ -2584,7 +2589,7 @@
         <v>3</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I17" s="24"/>
       <c r="J17" s="24"/>
@@ -2617,7 +2622,7 @@
         <v>4</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I18" s="24"/>
       <c r="J18" s="24"/>
@@ -2650,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="24"/>
       <c r="J19" s="24"/>
@@ -2683,7 +2688,7 @@
         <v>6</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
@@ -2716,7 +2721,7 @@
       <c r="H21" s="49"/>
       <c r="I21" s="49"/>
       <c r="J21" s="50" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K21" s="51"/>
       <c r="L21" s="52">
@@ -2759,7 +2764,7 @@
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="39"/>
       <c r="F22" s="39"/>
@@ -2767,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I22" s="53"/>
       <c r="J22" s="53"/>
@@ -2800,7 +2805,7 @@
         <v>2</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I23" s="24"/>
       <c r="J23" s="24"/>
@@ -2833,7 +2838,7 @@
         <v>3</v>
       </c>
       <c r="H24" s="55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I24" s="55"/>
       <c r="J24" s="55"/>
@@ -2866,7 +2871,7 @@
         <v>4</v>
       </c>
       <c r="H25" s="55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I25" s="55"/>
       <c r="J25" s="55"/>
@@ -2899,7 +2904,7 @@
         <v>5</v>
       </c>
       <c r="H26" s="55" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I26" s="55"/>
       <c r="J26" s="55"/>
@@ -2932,7 +2937,7 @@
         <v>6</v>
       </c>
       <c r="H27" s="30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
@@ -2965,7 +2970,7 @@
       <c r="H28" s="57"/>
       <c r="I28" s="57"/>
       <c r="J28" s="58" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K28" s="59"/>
       <c r="L28" s="60">
@@ -3008,7 +3013,7 @@
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="61" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E29" s="61"/>
       <c r="F29" s="61"/>
@@ -3016,7 +3021,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I29" s="53"/>
       <c r="J29" s="53"/>
@@ -3049,7 +3054,7 @@
         <v>2</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I30" s="24"/>
       <c r="J30" s="24"/>
@@ -3082,7 +3087,7 @@
         <v>3</v>
       </c>
       <c r="H31" s="55" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I31" s="55"/>
       <c r="J31" s="55"/>
@@ -3115,7 +3120,7 @@
         <v>4</v>
       </c>
       <c r="H32" s="55" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I32" s="55"/>
       <c r="J32" s="55"/>
@@ -3148,7 +3153,7 @@
         <v>5</v>
       </c>
       <c r="H33" s="55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I33" s="55"/>
       <c r="J33" s="55"/>
@@ -3181,7 +3186,7 @@
         <v>6</v>
       </c>
       <c r="H34" s="30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
@@ -3214,7 +3219,7 @@
       <c r="H35" s="63"/>
       <c r="I35" s="63"/>
       <c r="J35" s="64" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K35" s="65"/>
       <c r="L35" s="66">
@@ -3255,11 +3260,11 @@
     <row r="36" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="67" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C36" s="67"/>
       <c r="D36" s="68" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E36" s="68"/>
       <c r="F36" s="68"/>
@@ -3267,7 +3272,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="70" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I36" s="70"/>
       <c r="J36" s="70"/>
@@ -3300,7 +3305,7 @@
         <v>2</v>
       </c>
       <c r="H37" s="55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I37" s="55"/>
       <c r="J37" s="55"/>
@@ -3333,7 +3338,7 @@
         <v>3</v>
       </c>
       <c r="H38" s="55" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I38" s="55"/>
       <c r="J38" s="55"/>
@@ -3366,7 +3371,7 @@
         <v>4</v>
       </c>
       <c r="H39" s="55" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I39" s="55"/>
       <c r="J39" s="55"/>
@@ -3399,7 +3404,7 @@
         <v>5</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I40" s="24"/>
       <c r="J40" s="24"/>
@@ -3432,7 +3437,7 @@
         <v>6</v>
       </c>
       <c r="H41" s="73" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I41" s="73"/>
       <c r="J41" s="73"/>
@@ -3465,7 +3470,7 @@
       <c r="H42" s="78"/>
       <c r="I42" s="78"/>
       <c r="J42" s="79" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K42" s="80"/>
       <c r="L42" s="81">
@@ -3508,7 +3513,7 @@
       <c r="B43" s="67"/>
       <c r="C43" s="67"/>
       <c r="D43" s="82" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E43" s="82"/>
       <c r="F43" s="82"/>
@@ -3516,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I43" s="53"/>
       <c r="J43" s="53"/>
@@ -3549,7 +3554,7 @@
         <v>2</v>
       </c>
       <c r="H44" s="55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I44" s="55"/>
       <c r="J44" s="55"/>
@@ -3582,7 +3587,7 @@
         <v>3</v>
       </c>
       <c r="H45" s="55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I45" s="55"/>
       <c r="J45" s="55"/>
@@ -3615,7 +3620,7 @@
         <v>4</v>
       </c>
       <c r="H46" s="55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I46" s="55"/>
       <c r="J46" s="55"/>
@@ -3648,7 +3653,7 @@
         <v>5</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="24"/>
@@ -3681,7 +3686,7 @@
         <v>6</v>
       </c>
       <c r="H48" s="85" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I48" s="85"/>
       <c r="J48" s="85"/>
@@ -3714,7 +3719,7 @@
       <c r="H49" s="87"/>
       <c r="I49" s="87"/>
       <c r="J49" s="88" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K49" s="89"/>
       <c r="L49" s="90">
@@ -3757,7 +3762,7 @@
       <c r="B50" s="67"/>
       <c r="C50" s="67"/>
       <c r="D50" s="91" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E50" s="91"/>
       <c r="F50" s="91"/>
@@ -3765,7 +3770,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I50" s="41"/>
       <c r="J50" s="41"/>
@@ -3798,7 +3803,7 @@
         <v>2</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I51" s="24"/>
       <c r="J51" s="24"/>
@@ -3831,7 +3836,7 @@
         <v>3</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I52" s="24"/>
       <c r="J52" s="24"/>
@@ -3864,7 +3869,7 @@
         <v>4</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I53" s="24"/>
       <c r="J53" s="24"/>
@@ -3897,7 +3902,7 @@
         <v>5</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I54" s="24"/>
       <c r="J54" s="24"/>
@@ -3930,7 +3935,7 @@
         <v>6</v>
       </c>
       <c r="H55" s="30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I55" s="30"/>
       <c r="J55" s="30"/>
@@ -3963,7 +3968,7 @@
       <c r="H56" s="78"/>
       <c r="I56" s="78"/>
       <c r="J56" s="79" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K56" s="80"/>
       <c r="L56" s="81">
@@ -4006,7 +4011,7 @@
       <c r="B57" s="67"/>
       <c r="C57" s="67"/>
       <c r="D57" s="92" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E57" s="92"/>
       <c r="F57" s="92"/>
@@ -4014,7 +4019,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I57" s="53"/>
       <c r="J57" s="53"/>
@@ -4047,7 +4052,7 @@
         <v>2</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I58" s="24"/>
       <c r="J58" s="24"/>
@@ -4080,7 +4085,7 @@
         <v>3</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I59" s="24"/>
       <c r="J59" s="24"/>
@@ -4113,7 +4118,7 @@
         <v>4</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I60" s="24"/>
       <c r="J60" s="24"/>
@@ -4146,7 +4151,7 @@
         <v>5</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I61" s="24"/>
       <c r="J61" s="24"/>
@@ -4179,7 +4184,7 @@
         <v>6</v>
       </c>
       <c r="H62" s="85" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I62" s="85"/>
       <c r="J62" s="85"/>
@@ -4212,7 +4217,7 @@
       <c r="H63" s="93"/>
       <c r="I63" s="93"/>
       <c r="J63" s="94" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K63" s="95"/>
       <c r="L63" s="96">
@@ -4252,14 +4257,14 @@
     </row>
     <row r="64" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B64" s="97" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C64" s="97"/>
       <c r="D64" s="98" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E64" s="98"/>
       <c r="F64" s="98"/>
@@ -4267,7 +4272,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="41" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I64" s="41"/>
       <c r="J64" s="41"/>
@@ -4300,7 +4305,7 @@
         <v>2</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I65" s="24"/>
       <c r="J65" s="24"/>
@@ -4333,7 +4338,7 @@
         <v>3</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I66" s="24"/>
       <c r="J66" s="24"/>
@@ -4366,7 +4371,7 @@
         <v>4</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I67" s="24"/>
       <c r="J67" s="24"/>
@@ -4399,7 +4404,7 @@
         <v>5</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I68" s="24"/>
       <c r="J68" s="24"/>
@@ -4432,7 +4437,7 @@
         <v>6</v>
       </c>
       <c r="H69" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I69" s="30"/>
       <c r="J69" s="30"/>
@@ -4465,7 +4470,7 @@
       <c r="H70" s="35"/>
       <c r="I70" s="35"/>
       <c r="J70" s="36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K70" s="37"/>
       <c r="L70" s="38">
@@ -4508,7 +4513,7 @@
       <c r="B71" s="97"/>
       <c r="C71" s="97"/>
       <c r="D71" s="99" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E71" s="99"/>
       <c r="F71" s="99"/>
@@ -4516,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I71" s="53"/>
       <c r="J71" s="53"/>
@@ -4549,7 +4554,7 @@
         <v>2</v>
       </c>
       <c r="H72" s="55" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I72" s="55"/>
       <c r="J72" s="55"/>
@@ -4582,7 +4587,7 @@
         <v>3</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I73" s="24"/>
       <c r="J73" s="24"/>
@@ -4615,7 +4620,7 @@
         <v>4</v>
       </c>
       <c r="H74" s="55" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I74" s="55"/>
       <c r="J74" s="55"/>
@@ -4648,7 +4653,7 @@
         <v>5</v>
       </c>
       <c r="H75" s="55" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I75" s="55"/>
       <c r="J75" s="55"/>
@@ -4681,7 +4686,7 @@
         <v>6</v>
       </c>
       <c r="H76" s="85" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I76" s="85"/>
       <c r="J76" s="85"/>
@@ -4714,7 +4719,7 @@
       <c r="H77" s="101"/>
       <c r="I77" s="101"/>
       <c r="J77" s="102" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K77" s="103"/>
       <c r="L77" s="104">
@@ -4757,7 +4762,7 @@
       <c r="B78" s="97"/>
       <c r="C78" s="97"/>
       <c r="D78" s="99" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E78" s="99"/>
       <c r="F78" s="99"/>
@@ -4765,7 +4770,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="53" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I78" s="53"/>
       <c r="J78" s="53"/>
@@ -4798,7 +4803,7 @@
         <v>2</v>
       </c>
       <c r="H79" s="55" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I79" s="55"/>
       <c r="J79" s="55"/>
@@ -4831,7 +4836,7 @@
         <v>3</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I80" s="24"/>
       <c r="J80" s="24"/>
@@ -4864,7 +4869,7 @@
         <v>4</v>
       </c>
       <c r="H81" s="55" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I81" s="55"/>
       <c r="J81" s="55"/>
@@ -4897,7 +4902,7 @@
         <v>5</v>
       </c>
       <c r="H82" s="55" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I82" s="55"/>
       <c r="J82" s="55"/>
@@ -4930,7 +4935,7 @@
         <v>6</v>
       </c>
       <c r="H83" s="85" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I83" s="85"/>
       <c r="J83" s="85"/>
@@ -4963,7 +4968,7 @@
       <c r="H84" s="107"/>
       <c r="I84" s="107"/>
       <c r="J84" s="108" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K84" s="103"/>
       <c r="L84" s="104">
@@ -5004,11 +5009,11 @@
     <row r="85" ht="22" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" s="13"/>
       <c r="B85" s="109" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C85" s="109"/>
       <c r="D85" s="110" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E85" s="110"/>
       <c r="F85" s="110"/>
@@ -5016,11 +5021,11 @@
         <v>1</v>
       </c>
       <c r="H85" s="112" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I85" s="112"/>
       <c r="J85" s="113" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K85" s="111">
         <v>6</v>
@@ -5051,7 +5056,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="115" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I86" s="115"/>
       <c r="J86" s="116" t="str">
@@ -5087,7 +5092,7 @@
         <v>3</v>
       </c>
       <c r="H87" s="115" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I87" s="115"/>
       <c r="J87" s="116" t="str">
@@ -5123,7 +5128,7 @@
         <v>4</v>
       </c>
       <c r="H88" s="115" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I88" s="115"/>
       <c r="J88" s="116" t="str">
@@ -5159,11 +5164,11 @@
         <v>5</v>
       </c>
       <c r="H89" s="117" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I89" s="117"/>
       <c r="J89" s="118" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K89" s="25">
         <v>10</v>
@@ -5194,7 +5199,7 @@
       <c r="H90" s="123"/>
       <c r="I90" s="123"/>
       <c r="J90" s="124" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K90" s="125"/>
       <c r="L90" s="126">
@@ -5234,7 +5239,7 @@
     </row>
     <row r="91" ht="35.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" s="128" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B91" s="128"/>
       <c r="C91" s="128"/>
@@ -5243,11 +5248,11 @@
       <c r="F91" s="128"/>
       <c r="G91" s="128"/>
       <c r="H91" s="129" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I91" s="129"/>
       <c r="J91" s="130" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K91" s="130"/>
       <c r="L91" s="131">
@@ -5287,7 +5292,7 @@
     </row>
     <row r="92" ht="35.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" s="134" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B92" s="134"/>
       <c r="C92" s="135"/>
@@ -5296,11 +5301,11 @@
       <c r="F92" s="135"/>
       <c r="G92" s="135"/>
       <c r="H92" s="136" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I92" s="136"/>
       <c r="J92" s="137" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K92" s="137"/>
       <c r="L92" s="138"/>
@@ -5320,7 +5325,7 @@
     </row>
     <row r="93" ht="35.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" s="134" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B93" s="134"/>
       <c r="C93" s="135"/>
@@ -5329,11 +5334,11 @@
       <c r="F93" s="135"/>
       <c r="G93" s="135"/>
       <c r="H93" s="136" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I93" s="136"/>
       <c r="J93" s="140" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K93" s="140"/>
       <c r="L93" s="141"/>
@@ -5353,7 +5358,7 @@
     </row>
     <row r="94" ht="35.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" s="144" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B94" s="144"/>
       <c r="C94" s="145"/>
@@ -5362,7 +5367,7 @@
       <c r="F94" s="145"/>
       <c r="G94" s="145"/>
       <c r="H94" s="146" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I94" s="146"/>
       <c r="J94" s="140"/>
